--- a/data/starnet/starnet.xlsx
+++ b/data/starnet/starnet.xlsx
@@ -4808,82 +4808,82 @@
           <t>comment_text_8</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="25" t="inlineStr">
         <is>
           <t>comment_image_1</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="25" t="inlineStr">
         <is>
           <t>comment_image_alt_1</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="25" t="inlineStr">
         <is>
           <t>comment_image_2</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="25" t="inlineStr">
         <is>
           <t>comment_image_alt_2</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="25" t="inlineStr">
         <is>
           <t>comment_image_3</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="25" t="inlineStr">
         <is>
           <t>comment_image_alt_3</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="25" t="inlineStr">
         <is>
           <t>comment_image_4</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="25" t="inlineStr">
         <is>
           <t>comment_image_alt_4</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="25" t="inlineStr">
         <is>
           <t>comment_image_5</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="25" t="inlineStr">
         <is>
           <t>comment_image_alt_5</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="25" t="inlineStr">
         <is>
           <t>comment_image_6</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="25" t="inlineStr">
         <is>
           <t>comment_image_alt_6</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="25" t="inlineStr">
         <is>
           <t>comment_image_7</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="25" t="inlineStr">
         <is>
           <t>comment_image_alt_7</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="25" t="inlineStr">
         <is>
           <t>comment_image_8</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="25" t="inlineStr">
         <is>
           <t>comment_image_alt_8</t>
         </is>
@@ -5717,8 +5717,16 @@
       <c r="E19" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n"/>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>assets/starnet-liexingzu-michelin-guide.png</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>米其林餐厅名单（MICHELIN 八家餐厅）同人配图</t>
+        </is>
+      </c>
       <c r="H19" s="16" t="n"/>
       <c r="I19" s="7" t="inlineStr">
         <is>
@@ -6123,12 +6131,12 @@
       <c r="U27" s="16" t="n"/>
       <c r="V27" s="16" t="n"/>
       <c r="W27" s="16" t="n"/>
-      <c r="X27" t="inlineStr">
+      <c r="X27" s="25" t="inlineStr">
         <is>
           <t>assets/starnet-comment-ridiculous.gif</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y27" s="25" t="inlineStr">
         <is>
           <t>ridiculous 表情包</t>
         </is>
@@ -6532,8 +6540,16 @@
       <c r="E36" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="16" t="n"/>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>assets/starnet-altair-phony-lyrics-card.png</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>「Phony」歌词卡 · Altair - CONSTELL</t>
+        </is>
+      </c>
       <c r="H36" s="16" t="n"/>
       <c r="I36" s="7" t="inlineStr">
         <is>

--- a/data/starnet/starnet.xlsx
+++ b/data/starnet/starnet.xlsx
@@ -6262,7 +6262,7 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>抢到票了！也期待这一次的见面～</t>
+          <t>抢到票了！晒下之前的票根，也期待这一次的见面～</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -6270,8 +6270,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F30" s="19" t="n"/>
-      <c r="G30" s="19" t="n"/>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>assets/starnet-zhuiguangzu-constell-ticket-stubs.png</t>
+        </is>
+      </c>
+      <c r="G30" s="19" t="inlineStr">
+        <is>
+          <t>CONSTELL 一至三场演唱会票根（启明星／遨游／临界点）</t>
+        </is>
+      </c>
       <c r="H30" s="19" t="n"/>
       <c r="I30" s="12" t="inlineStr">
         <is>
